--- a/Eszközök/Forrás/vezetőség.xlsx
+++ b/Eszközök/Forrás/vezetőség.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20402"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Bence\Dokumentumok\Visual Studio 2022\Repos\GitHub\IskolaAPI\IskolaAPI2\Feladat\Forrás\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\boros.bence\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D7228EF-5450-4D6A-AB32-AF788BD3F592}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDC02EE0-9052-4037-ADEC-FBD670284F75}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12555" yWindow="1395" windowWidth="16245" windowHeight="11415" xr2:uid="{56399AD0-3493-48D7-B319-F438A9747BAE}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16800" windowHeight="7950" xr2:uid="{56399AD0-3493-48D7-B319-F438A9747BAE}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -20,15 +20,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -63,12 +54,6 @@
     <t>pedagógiai igazgatóhelyettes</t>
   </si>
   <si>
-    <t>Király-Török Annamária</t>
-  </si>
-  <si>
-    <t>kiraly.annamaria@vasvari.org</t>
-  </si>
-  <si>
     <t>molnar.edit@vasvari.org</t>
   </si>
   <si>
@@ -82,6 +67,12 @@
   </si>
   <si>
     <t>kadar.blanka@vasvari.org</t>
+  </si>
+  <si>
+    <t>Murár Zoltán</t>
+  </si>
+  <si>
+    <t>murar.zoltan@vasvari.org</t>
   </si>
 </sst>
 </file>
@@ -436,13 +427,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{849D957D-3D96-42DC-BEAD-33C659943514}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -456,21 +447,21 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -484,32 +475,32 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" t="s">
         <v>11</v>
-      </c>
-      <c r="D5" t="s">
-        <v>13</v>
       </c>
     </row>
   </sheetData>
